--- a/test-env/data/recommendations.xlsx
+++ b/test-env/data/recommendations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariano/Documents/projects/k8s-rightsizer/test-env/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722332D8-AE4F-074A-B829-FFC40016B759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AD6471-CC85-1F4C-9B93-975D82D10945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="58">
   <si>
     <t>Environment</t>
   </si>
@@ -144,9 +144,6 @@
     <t>8000m</t>
   </si>
   <si>
-    <t>16Gi</t>
-  </si>
-  <si>
     <t>test-paused-workload</t>
   </si>
   <si>
@@ -162,12 +159,6 @@
     <t>app-container</t>
   </si>
   <si>
-    <t>0Mi</t>
-  </si>
-  <si>
-    <t>0m</t>
-  </si>
-  <si>
     <t>test-sts-standard</t>
   </si>
   <si>
@@ -205,6 +196,27 @@
   </si>
   <si>
     <t>test-workload-strategy</t>
+  </si>
+  <si>
+    <t>48Mi</t>
+  </si>
+  <si>
+    <t>95Mi</t>
+  </si>
+  <si>
+    <t>20m</t>
+  </si>
+  <si>
+    <t>96Mi</t>
+  </si>
+  <si>
+    <t>10Mi</t>
+  </si>
+  <si>
+    <t>16000Mi</t>
+  </si>
+  <si>
+    <t>32000Mi</t>
   </si>
 </sst>
 </file>
@@ -306,7 +318,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -327,6 +339,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{875B3D47-7E8A-4A9A-9CCE-2B38D6005361}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" style="4" customWidth="1"/>
@@ -639,9 +654,9 @@
     <col min="3" max="3" width="29.33203125" style="4" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="4" customWidth="1"/>
     <col min="5" max="5" width="28.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" style="4"/>
-    <col min="7" max="7" width="24" style="4" customWidth="1"/>
-    <col min="8" max="8" width="21.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="0" style="4" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="24" style="4" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" style="4" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="38" style="4" customWidth="1"/>
     <col min="10" max="10" width="33.83203125" style="4" customWidth="1"/>
     <col min="11" max="11" width="21" style="4" customWidth="1"/>
@@ -659,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -697,36 +712,36 @@
     </row>
     <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>40</v>
+      <c r="J2" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>39</v>
+      <c r="N2" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -735,56 +750,56 @@
         <v>22</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>40</v>
+      <c r="J3" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>39</v>
+      <c r="N3" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>40</v>
+      <c r="J4" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>13</v>
@@ -796,140 +811,140 @@
         <v>21</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>40</v>
+      <c r="J5" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>40</v>
+      <c r="J6" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>27</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>40</v>
+      <c r="J7" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>40</v>
+      <c r="J8" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>40</v>
+      <c r="J9" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>13</v>
@@ -938,27 +953,27 @@
         <v>15</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>40</v>
+      <c r="J10" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>39</v>
+      <c r="N10" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>13</v>
@@ -967,27 +982,27 @@
         <v>15</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>40</v>
+      <c r="J11" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>13</v>
@@ -996,27 +1011,27 @@
         <v>15</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>13</v>
@@ -1025,27 +1040,27 @@
         <v>15</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>13</v>
@@ -1054,27 +1069,27 @@
         <v>15</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>40</v>
+      <c r="J14" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="M14" s="8" t="s">
         <v>27</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>13</v>
@@ -1083,27 +1098,27 @@
         <v>15</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="M15" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>13</v>
@@ -1112,23 +1127,73 @@
         <v>15</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>39</v>
-      </c>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="D20" s="8"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="4:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="D21" s="8"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="4:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="D22" s="8"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23" spans="4:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="D23" s="10"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" spans="4:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="D24" s="8"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1" xr:uid="{875B3D47-7E8A-4A9A-9CCE-2B38D6005361}"/>
@@ -1318,18 +1383,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1352,18 +1417,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0BB01DB-2273-48CA-9212-17EA76FB34AA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA8BD82F-AA6D-48FD-8510-6ED9BD04899D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0BB01DB-2273-48CA-9212-17EA76FB34AA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>